--- a/R_analysis/output/supplementary/Tabela_Supl_Comparacao_Metodos.xlsx
+++ b/R_analysis/output/supplementary/Tabela_Supl_Comparacao_Metodos.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (casos)</t>
+          <t>Brasil — Gestational (casos)</t>
         </is>
       </c>
       <c r="B2">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional (casos)</t>
+          <t>Brasil — Gestational (casos)</t>
         </is>
       </c>
       <c r="B3">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B4">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B5">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B6">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brasil — Congênita (casos)</t>
+          <t>Brasil — Congenital (casos)</t>
         </is>
       </c>
       <c r="B7">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B8">
@@ -531,7 +531,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B9">
@@ -552,7 +552,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B10">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B11">
@@ -594,7 +594,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B12">
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B13">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B14">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B15">
@@ -678,7 +678,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B16">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B17">
@@ -720,7 +720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B18">
@@ -741,7 +741,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B19">
@@ -762,7 +762,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B20">
@@ -783,7 +783,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B21">
@@ -804,7 +804,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B22">
@@ -825,7 +825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B23">
@@ -846,7 +846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B24">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B25">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B26">
@@ -909,7 +909,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B27">
@@ -930,7 +930,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B28">
@@ -951,7 +951,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B29">
@@ -972,7 +972,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B30">
@@ -993,7 +993,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B31">
@@ -1014,7 +1014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B32">
